--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.37779499554216</v>
+        <v>7.536391686775601</v>
       </c>
       <c r="D2" t="n">
-        <v>12.23076388536214</v>
+        <v>1.987499131371348</v>
       </c>
       <c r="E2" t="n">
-        <v>6.544495315390011</v>
+        <v>1.063480488750876</v>
       </c>
       <c r="F2" t="n">
-        <v>7.68193588485478</v>
+        <v>1.248314581288902</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.36810430221717</v>
+        <v>6.55981694911029</v>
       </c>
       <c r="D3" t="n">
-        <v>19.77259156500379</v>
+        <v>3.213046129313117</v>
       </c>
       <c r="E3" t="n">
-        <v>6.544495315390011</v>
+        <v>1.063480488750876</v>
       </c>
       <c r="F3" t="n">
-        <v>7.68193588485478</v>
+        <v>1.248314581288902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.5024563200616</v>
+        <v>4.95664915201001</v>
       </c>
       <c r="D4" t="n">
-        <v>30.9313546025816</v>
+        <v>5.02634512291951</v>
       </c>
       <c r="E4" t="n">
-        <v>6.544495315390011</v>
+        <v>1.063480488750876</v>
       </c>
       <c r="F4" t="n">
-        <v>7.68193588485478</v>
+        <v>1.248314581288902</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
